--- a/tame_output/ON/bt/strategyON_20240630.xlsx
+++ b/tame_output/ON/bt/strategyON_20240630.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-522.8%</t>
+          <t>-522.7%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.5%</t>
+          <t>-164.6%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-211.1%</t>
+          <t>-211.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-199.6%</t>
+          <t>-199.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1405,11 +1405,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2009"/>
+  <dimension ref="A1:G2010"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710557061743829</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
         <v>3.56270314625311</v>
@@ -47768,6 +47768,29 @@
       </c>
       <c r="G2009" t="n">
         <v>3.709268455193393</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="2" t="n">
+        <v>45472</v>
+      </c>
+      <c r="B2010" t="n">
+        <v>3.711937966511798</v>
+      </c>
+      <c r="C2010" t="n">
+        <v>3.561137156463262</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>-3.61087880998903</v>
+      </c>
+      <c r="E2010" t="n">
+        <v>2.116429208153903</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>0.2455437415719411</v>
+      </c>
+      <c r="G2010" t="n">
+        <v>3.708463401406427</v>
       </c>
     </row>
   </sheetData>
